--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB3797F-5F9D-455B-9D1F-AD86BB3D37DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E726CF3-D9A3-43F6-88C3-95836E958DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 19-12-2025'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 29-01-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E726CF3-D9A3-43F6-88C3-95836E958DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CA3C97-83E8-4490-874C-77C70DCA0F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 29-01-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 02-02-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CA3C97-83E8-4490-874C-77C70DCA0F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFEE33B-8599-4447-96D5-19F2DD21B9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 02-02-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 20-02-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFEE33B-8599-4447-96D5-19F2DD21B9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC42C8D-E702-44B6-AC0B-5D1BD870DA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 20-02-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 04-03-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC42C8D-E702-44B6-AC0B-5D1BD870DA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B918D818-3692-4B4D-AEB0-37FD72987085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 04-03-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 06-03-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B918D818-3692-4B4D-AEB0-37FD72987085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E62BC83-CC36-4E11-84CF-970F4556C83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E62BC83-CC36-4E11-84CF-970F4556C83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767E641C-611B-41F5-AC68-BA60E63D016F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767E641C-611B-41F5-AC68-BA60E63D016F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A3BC63-6B8B-4F3B-9943-04C593D3C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 06-03-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 09-03-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A3BC63-6B8B-4F3B-9943-04C593D3C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFE381E-3542-4876-865C-AC4A1791E8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFE381E-3542-4876-865C-AC4A1791E8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7B6235-23B3-49B2-AA2F-7486DA5131E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 09-03-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 11-03-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7B6235-23B3-49B2-AA2F-7486DA5131E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB351E6-76DA-4731-A413-810C9FB175D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB351E6-76DA-4731-A413-810C9FB175D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8256B60C-1A48-4A77-898E-44F949E84F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 11-03-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 20-03-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8256B60C-1A48-4A77-898E-44F949E84F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE7DB4D-0B0F-47B5-8923-788ECE8009AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 20-03-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 25-03-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE7DB4D-0B0F-47B5-8923-788ECE8009AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B635A0-7175-40B3-A146-31E9C0920015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 25-03-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 08-04-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B635A0-7175-40B3-A146-31E9C0920015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3F1A24-B436-4DA0-92A1-6B159B8BB5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 08-04-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 10-04-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3F1A24-B436-4DA0-92A1-6B159B8BB5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AADB66-718C-4702-A6A4-0B2FB4BF6683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AADB66-718C-4702-A6A4-0B2FB4BF6683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C942A130-5577-4558-8C48-9FE175C39F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 10-04-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 14-04-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C942A130-5577-4558-8C48-9FE175C39F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9F6B19-B968-4E1E-AD91-BE0E39908978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 14-04-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 24-04-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9F6B19-B968-4E1E-AD91-BE0E39908978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C9C575-1C3B-408C-964C-1801D6410427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C9C575-1C3B-408C-964C-1801D6410427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5962FB5-6816-49DE-B252-66088C1EA2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 24-04-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 27-04-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5962FB5-6816-49DE-B252-66088C1EA2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007D5442-C560-46F1-AA8F-4A7F40BC2B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 27-04-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 06-05-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007D5442-C560-46F1-AA8F-4A7F40BC2B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B06DEEC-14A6-43BE-B671-5AAD2B00AA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 06-05-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 01-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B06DEEC-14A6-43BE-B671-5AAD2B00AA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85752D26-F73B-4B8B-B524-28CEA0120668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 01-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 02-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85752D26-F73B-4B8B-B524-28CEA0120668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C4B9A7-8EC6-42AA-A9EB-B7C88AE3FA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C4B9A7-8EC6-42AA-A9EB-B7C88AE3FA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF37274-912F-457D-880D-D49F5527B1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 02-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 05-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E726CF3-D9A3-43F6-88C3-95836E958DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A41A161-477B-4FC4-9C9F-392245C72B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DEFE27-AE0F-4026-BD24-09287E6CA021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5547908D-593A-418B-B778-4139C96226AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5547908D-593A-418B-B778-4139C96226AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1D6622-91F6-4888-9F09-FB7AC9D631E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1D6622-91F6-4888-9F09-FB7AC9D631E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEA4BDC-AE78-4905-B7E5-44CC0E7BE11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 09-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 15-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEA4BDC-AE78-4905-B7E5-44CC0E7BE11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB3A689-9B1B-4064-884F-6DA816451C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 15-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 22-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB3A689-9B1B-4064-884F-6DA816451C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2AF33-ED25-4CD1-BE30-D1E90646EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 22-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 23-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2AF33-ED25-4CD1-BE30-D1E90646EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3B6A57-132F-446D-AF64-7A537C812573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB3A689-9B1B-4064-884F-6DA816451C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9389AFD-1662-4347-8D56-A2FCCE3A574A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 22-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 23-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9389AFD-1662-4347-8D56-A2FCCE3A574A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096FE6D8-4373-4FBB-8C5B-4C5C5D64DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 23-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 25-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096FE6D8-4373-4FBB-8C5B-4C5C5D64DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD932872-F52A-4E55-A542-4950E88AA057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 25-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 30-06-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD932872-F52A-4E55-A542-4950E88AA057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4A544D-B00C-4001-891E-B33302097D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4A544D-B00C-4001-891E-B33302097D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F01DC44-9DF4-4469-981C-A1668392A74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 30-06-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 01-07-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F01DC44-9DF4-4469-981C-A1668392A74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2148FE-94E9-4A43-B91B-A0133C4BBF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 01-07-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 02-07-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F01DC44-9DF4-4469-981C-A1668392A74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B695E9B-E372-48C7-85C2-B90C48262811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 01-07-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 03-07-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2148FE-94E9-4A43-B91B-A0133C4BBF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD2887A-2C63-42AF-86B7-758C3B49A9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 02-07-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 03-07-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD2887A-2C63-42AF-86B7-758C3B49A9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E1D108-FD6B-4D5F-9286-4F92941A910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 03-07-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 09-07-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E1D108-FD6B-4D5F-9286-4F92941A910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F02B4A-AAAB-480C-A63E-E1FDE3B1A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 09-07-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 19-08-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F02B4A-AAAB-480C-A63E-E1FDE3B1A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB67BD7-61FF-4DC6-A7AC-2C582732CB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 19-08-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 21-08-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB67BD7-61FF-4DC6-A7AC-2C582732CB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE891F50-30A3-4AC6-BC06-8997FC429A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 21-08-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 27-08-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE891F50-30A3-4AC6-BC06-8997FC429A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8361C-C1CA-4B61-A823-12D8C424AF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 27-08-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 02-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8361C-C1CA-4B61-A823-12D8C424AF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2F332B-28CF-430E-B954-757E87B64EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 02-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 06-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2F332B-28CF-430E-B954-757E87B64EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945DC18E-BD2D-4DB9-BB0E-45FBB0680B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945DC18E-BD2D-4DB9-BB0E-45FBB0680B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB7243-EF03-4A34-AECB-E903942E2BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 06-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 07-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB7243-EF03-4A34-AECB-E903942E2BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818C67B8-2CCB-4446-8DBF-59E4BC40A018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 07-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 09-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818C67B8-2CCB-4446-8DBF-59E4BC40A018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1656C4-B6F0-4682-BFD6-B9D17A960D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
